--- a/branches/release/2027.0.0-ballot.rc2/StructureDefinition-mii-pr-molgen-molekularer-biomarker.xlsx
+++ b/branches/release/2027.0.0-ballot.rc2/StructureDefinition-mii-pr-molgen-molekularer-biomarker.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T11:45:55+00:00</t>
+    <t>2026-09-04T12:05:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/release/2027.0.0-ballot.rc2/StructureDefinition-mii-pr-molgen-molekularer-biomarker.xlsx
+++ b/branches/release/2027.0.0-ballot.rc2/StructureDefinition-mii-pr-molgen-molekularer-biomarker.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T12:05:45+00:00</t>
+    <t>2026-09-04T13:46:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/release/2027.0.0-ballot.rc2/StructureDefinition-mii-pr-molgen-molekularer-biomarker.xlsx
+++ b/branches/release/2027.0.0-ballot.rc2/StructureDefinition-mii-pr-molgen-molekularer-biomarker.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T13:46:18+00:00</t>
+    <t>2026-09-04T15:11:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
